--- a/content/jamo.xlsx
+++ b/content/jamo.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자모 조합" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연습" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -536,7 +537,19 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>연습 시트</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>튜토리얼(육조거리) 연습 판의 문장 하나(J00 「알현」). 본편 11개와 섞지 않으려고 시트를 따로 뒀다. 갈무리 판·PDF에는 넣지 않는다(2026-09-23).</t>
         </is>
       </c>
     </row>
@@ -1188,4 +1201,145 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>문</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>빗장</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>낱말</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>문장</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>문장 앞</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>문장 뒤</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>음절 수</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>자모 수</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>자모</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>육조거리(연습)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>알현</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>임금처럼 지위가 높고 귀한 사람을 찾아가 뵙는 것을 알현이라고 한다.</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임금처럼 지위가 높고 귀한 사람을 찾아가 뵙는 것을 </t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>이라고 한다.</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>ㅇ ㅏ ㄹ / ㅎ ㅕ ㄴ</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>✅ 2026-09-23 🙋 "초안 좋아." · 📜 표준국어대사전 「알현(謁見)」 "지체가 높고 귀한 사람을 찾아가 뵘." · 튜토리얼 연습 판 · 갈무리·PDF에는 넣지 않는다</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>